--- a/monthly_report.xlsx
+++ b/monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <t>business_date</t>
   </si>
@@ -39,6 +39,12 @@
     <t>member_rank</t>
   </si>
   <si>
+    <t>Worku Guta</t>
+  </si>
+  <si>
+    <t>Dajane Guta</t>
+  </si>
+  <si>
     <t>Walfana Megersa</t>
   </si>
   <si>
@@ -48,21 +54,12 @@
     <t>Kenanisa Bikila</t>
   </si>
   <si>
-    <t>Dajane Guta</t>
+    <t>Salamon Zarihun</t>
   </si>
   <si>
     <t>Lami Diro</t>
   </si>
   <si>
-    <t>Salamon Zarihun</t>
-  </si>
-  <si>
-    <t>NULL</t>
-  </si>
-  <si>
-    <t>Worku Guta</t>
-  </si>
-  <si>
     <t>Barsisa Merga</t>
   </si>
   <si>
@@ -72,49 +69,46 @@
     <t>Geetu Bekela</t>
   </si>
   <si>
+    <t>Silash Dabesa</t>
+  </si>
+  <si>
     <t>Abera Asefa</t>
   </si>
   <si>
+    <t>Naggasaa Dheeressaa</t>
+  </si>
+  <si>
+    <t>Worku Bekele</t>
+  </si>
+  <si>
     <t>Warkitu Dilba</t>
   </si>
   <si>
     <t>Boki Bayena</t>
   </si>
   <si>
-    <t>Worku Bekele</t>
-  </si>
-  <si>
     <t>Lalise Megersa</t>
   </si>
   <si>
     <t>Warki Lemma</t>
   </si>
   <si>
-    <t>Silash Dabesa</t>
-  </si>
-  <si>
-    <t>Naggasaa Dheeressaa</t>
-  </si>
-  <si>
     <t>Alamuu Guutaa</t>
   </si>
   <si>
     <t>Milkesa Gebre</t>
   </si>
   <si>
-    <t>Nabiyat Habtewold</t>
-  </si>
-  <si>
     <t>Chaluma Uma</t>
   </si>
   <si>
     <t>Katamaa Diroo</t>
   </si>
   <si>
+    <t>Jaalataa magarsaa</t>
+  </si>
+  <si>
     <t>Mange Lammaa</t>
-  </si>
-  <si>
-    <t>Jaalataa magarsaa</t>
   </si>
   <si>
     <t>***</t>
@@ -928,11 +922,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -957,10 +950,10 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
-        <v>46171</v>
+        <v>46203</v>
       </c>
       <c r="B2">
-        <v>1002</v>
+        <v>1024</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -969,7 +962,7 @@
         <v>1000</v>
       </c>
       <c r="E2">
-        <v>150000</v>
+        <v>199000</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -977,10 +970,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>46170</v>
+        <v>46202</v>
       </c>
       <c r="B3">
-        <v>1003</v>
+        <v>1012</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
@@ -989,18 +982,18 @@
         <v>1000</v>
       </c>
       <c r="E3">
-        <v>150000</v>
+        <v>153500</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>46168</v>
+        <v>46199</v>
       </c>
       <c r="B4">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -1009,7 +1002,7 @@
         <v>1000</v>
       </c>
       <c r="E4">
-        <v>125000</v>
+        <v>151000</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -1017,10 +1010,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <v>46172</v>
+        <v>46199</v>
       </c>
       <c r="B5">
-        <v>1012</v>
+        <v>1003</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
@@ -1029,18 +1022,18 @@
         <v>1000</v>
       </c>
       <c r="E5">
-        <v>123500</v>
+        <v>151000</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>46167</v>
+        <v>46199</v>
       </c>
       <c r="B6">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -1049,15 +1042,15 @@
         <v>1000</v>
       </c>
       <c r="E6">
-        <v>123000</v>
+        <v>151000</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <v>46175</v>
+        <v>46202</v>
       </c>
       <c r="B7">
         <v>1010</v>
@@ -1069,27 +1062,27 @@
         <v>1000</v>
       </c>
       <c r="E7">
-        <v>106000</v>
+        <v>151000</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B8">
+        <v>1008</v>
+      </c>
+      <c r="C8" t="s">
         <v>12</v>
       </c>
-      <c r="B8">
-        <v>1024</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
       <c r="D8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E8">
-        <v>101000</v>
+        <v>124000</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -1097,19 +1090,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <v>46171</v>
+        <v>46203</v>
       </c>
       <c r="B9">
         <v>1014</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D9">
         <v>1000</v>
       </c>
       <c r="E9">
-        <v>87000</v>
+        <v>88000</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -1117,19 +1110,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <v>46169</v>
+        <v>46199</v>
       </c>
       <c r="B10">
         <v>1013</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D10">
         <v>1000</v>
       </c>
       <c r="E10">
-        <v>86000</v>
+        <v>87000</v>
       </c>
       <c r="F10">
         <v>9</v>
@@ -1137,19 +1130,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <v>46171</v>
+        <v>46199</v>
       </c>
       <c r="B11">
         <v>1001</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11">
         <v>1000</v>
       </c>
       <c r="E11">
-        <v>75000</v>
+        <v>76000</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -1157,19 +1150,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <v>46172</v>
+        <v>46200</v>
       </c>
       <c r="B12">
-        <v>1015</v>
+        <v>1004</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D12">
         <v>1000</v>
       </c>
       <c r="E12">
-        <v>73000</v>
+        <v>74000</v>
       </c>
       <c r="F12">
         <v>11</v>
@@ -1177,39 +1170,39 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <v>46167</v>
+        <v>46200</v>
       </c>
       <c r="B13">
-        <v>1005</v>
+        <v>1015</v>
       </c>
       <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13">
+        <v>1000</v>
+      </c>
+      <c r="E13">
+        <v>74000</v>
+      </c>
+      <c r="F13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B14">
+        <v>1017</v>
+      </c>
+      <c r="C14" t="s">
         <v>18</v>
       </c>
-      <c r="D13">
-        <v>1000</v>
-      </c>
-      <c r="E13">
-        <v>51500</v>
-      </c>
-      <c r="F13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14">
-        <v>1009</v>
-      </c>
-      <c r="C14" t="s">
-        <v>19</v>
-      </c>
       <c r="D14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E14">
-        <v>50500</v>
+        <v>56600</v>
       </c>
       <c r="F14">
         <v>13</v>
@@ -1217,19 +1210,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <v>46171</v>
+        <v>46199</v>
       </c>
       <c r="B15">
         <v>1022</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D15">
         <v>1000</v>
       </c>
       <c r="E15">
-        <v>50000</v>
+        <v>56000</v>
       </c>
       <c r="F15">
         <v>14</v>
@@ -1237,19 +1230,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <v>46172</v>
+        <v>46199</v>
       </c>
       <c r="B16">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D16">
         <v>1000</v>
       </c>
       <c r="E16">
-        <v>49500</v>
+        <v>52500</v>
       </c>
       <c r="F16">
         <v>15</v>
@@ -1257,19 +1250,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <v>46171</v>
+        <v>46200</v>
       </c>
       <c r="B17">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D17">
         <v>1000</v>
       </c>
       <c r="E17">
-        <v>49500</v>
+        <v>52500</v>
       </c>
       <c r="F17">
         <v>15</v>
@@ -1277,19 +1270,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <v>46176</v>
+        <v>46202</v>
       </c>
       <c r="B18">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D18">
         <v>1000</v>
       </c>
       <c r="E18">
-        <v>48500</v>
+        <v>50500</v>
       </c>
       <c r="F18">
         <v>17</v>
@@ -1297,39 +1290,39 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <v>46168</v>
+        <v>46200</v>
       </c>
       <c r="B19">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D19">
         <v>1000</v>
       </c>
       <c r="E19">
-        <v>46000</v>
+        <v>50500</v>
       </c>
       <c r="F19">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>12</v>
+      <c r="A20" s="1">
+        <v>46204</v>
       </c>
       <c r="B20">
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E20">
-        <v>45000</v>
+        <v>47000</v>
       </c>
       <c r="F20">
         <v>19</v>
@@ -1337,36 +1330,36 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <v>46172</v>
+        <v>46204</v>
       </c>
       <c r="B21">
         <v>1023</v>
       </c>
       <c r="C21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21">
+        <v>1000</v>
+      </c>
+      <c r="E21">
+        <v>46000</v>
+      </c>
+      <c r="F21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B22">
+        <v>1020</v>
+      </c>
+      <c r="C22" t="s">
         <v>26</v>
       </c>
-      <c r="D21">
-        <v>1000</v>
-      </c>
-      <c r="E21">
-        <v>45000</v>
-      </c>
-      <c r="F21">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22">
-        <v>1019</v>
-      </c>
-      <c r="C22" t="s">
-        <v>27</v>
-      </c>
       <c r="D22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E22">
         <v>44000</v>
@@ -1377,102 +1370,82 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <v>46172</v>
+        <v>46200</v>
       </c>
       <c r="B23">
-        <v>1020</v>
+        <v>1026</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D23">
         <v>1000</v>
       </c>
       <c r="E23">
-        <v>43000</v>
+        <v>44000</v>
       </c>
       <c r="F23">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <v>46170</v>
+        <v>46200</v>
       </c>
       <c r="B24">
-        <v>1026</v>
+        <v>1018</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>1000</v>
       </c>
       <c r="E24">
-        <v>43000</v>
+        <v>42000</v>
       </c>
       <c r="F24">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <v>46171</v>
+        <v>46200</v>
       </c>
       <c r="B25">
         <v>1025</v>
       </c>
       <c r="C25" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25">
+        <v>1000</v>
+      </c>
+      <c r="E25">
+        <v>42000</v>
+      </c>
+      <c r="F25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>30</v>
       </c>
-      <c r="D25">
-        <v>1000</v>
-      </c>
-      <c r="E25">
-        <v>41000</v>
-      </c>
-      <c r="F25">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
-        <v>46171</v>
-      </c>
-      <c r="B26">
-        <v>1018</v>
+      <c r="B26" t="s">
+        <v>30</v>
       </c>
       <c r="C26" t="s">
         <v>31</v>
       </c>
       <c r="D26">
-        <v>1000</v>
+        <v>24000</v>
       </c>
       <c r="E26">
-        <v>1000</v>
-      </c>
-      <c r="F26">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27">
-        <v>21000</v>
-      </c>
-      <c r="E27">
-        <v>1786000</v>
-      </c>
-      <c r="F27" t="s">
-        <v>32</v>
+        <v>2039100</v>
+      </c>
+      <c r="F26" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
